--- a/astro-site/public/dl/guia-panaderia-obrador/calculadora-capex.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/calculadora-capex.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX Panadería" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'CAPEX Panadería'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -462,7 +464,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -481,6 +483,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -531,7 +534,6 @@
       <c r="C5" t="n">
         <v>48000</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Suelo, paredes, electricidad obrador</t>
@@ -550,7 +552,6 @@
       <c r="C6" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Crítico licencia clasificada</t>
@@ -569,7 +570,6 @@
       <c r="C7" t="n">
         <v>12000</v>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Obrador requiere extracción potente</t>
@@ -599,7 +599,6 @@
       <c r="C9" t="n">
         <v>28000</v>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Polín, Salva, Logiudice</t>
@@ -618,7 +617,6 @@
       <c r="C10" t="n">
         <v>35000</v>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Si volumen alto, complementa horno piso</t>
@@ -637,7 +635,6 @@
       <c r="C11" t="n">
         <v>7000</v>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Ferneto, Sottoriva, Salva</t>
@@ -656,7 +653,6 @@
       <c r="C12" t="n">
         <v>15000</v>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Frío + calor + humedad</t>
@@ -675,7 +671,6 @@
       <c r="C13" t="n">
         <v>8000</v>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Salva, Sottoriva</t>
@@ -694,8 +689,6 @@
       <c r="C14" t="n">
         <v>9000</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -709,7 +702,6 @@
       <c r="C15" t="n">
         <v>18000</v>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Solo si haces bollería laminada</t>
@@ -728,7 +720,6 @@
       <c r="C16" t="n">
         <v>11000</v>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>MP positiva + masa cruda</t>
@@ -747,7 +738,6 @@
       <c r="C17" t="n">
         <v>9600</v>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>600-1.200€ unidad</t>
@@ -766,8 +756,6 @@
       <c r="C18" t="n">
         <v>5000</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -781,8 +769,6 @@
       <c r="C19" t="n">
         <v>4500</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -807,7 +793,6 @@
       <c r="C21" t="n">
         <v>9000</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Edenox, Infrico</t>
@@ -826,7 +811,6 @@
       <c r="C22" t="n">
         <v>12000</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Estanterías madera + caja</t>
@@ -845,7 +829,6 @@
       <c r="C23" t="n">
         <v>3000</v>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Cálida 2700-3000K</t>
@@ -875,7 +858,6 @@
       <c r="C25" t="n">
         <v>8000</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Logo, packaging, fotos producto</t>
@@ -894,7 +876,6 @@
       <c r="C26" t="n">
         <v>6000</v>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Mejor stock corto + reposición frecuente</t>
@@ -913,7 +894,6 @@
       <c r="C27" t="n">
         <v>12000</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>2-3 meses alquiler de aval</t>
@@ -932,7 +912,6 @@
       <c r="C28" t="n">
         <v>8000</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Clasificada + RGSEAA + manipulador</t>
@@ -951,20 +930,13 @@
       <c r="C29" t="n">
         <v>30000</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Caja seguridad mientras alcanzas break-even</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -973,22 +945,30 @@
       </c>
       <c r="B31">
         <f>SUM(B4:B27)</f>
-        <v/>
+        <v>113700.0</v>
       </c>
       <c r="C31">
         <f>SUM(C4:C27)</f>
-        <v/>
+        <v>278100.0</v>
       </c>
       <c r="D31">
         <f>SUM(D4:D27)</f>
-        <v/>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>